--- a/04_Figures/F04_association/modules/trajectory/wilcoxon/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/trajectory/wilcoxon/c_data/results.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -66,12 +66,6 @@
     <t xml:space="preserve">ME_red@T1</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_salmon@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan@T1</t>
-  </si>
-  <si>
     <t xml:space="preserve">ME_turquoise@T1</t>
   </si>
   <si>
@@ -105,12 +99,6 @@
     <t xml:space="preserve">ME_red@T2</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_salmon@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan@T2</t>
-  </si>
-  <si>
     <t xml:space="preserve">ME_turquoise@T2</t>
   </si>
   <si>
@@ -142,12 +130,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan@T3</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise@T3</t>
@@ -546,14 +528,14 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0972656897772912</v>
+        <v>-0.113889138401406</v>
       </c>
       <c r="E2"/>
       <c r="F2" t="n">
-        <v>0.754578754578755</v>
+        <v>0.228438228438228</v>
       </c>
       <c r="G2" t="n">
-        <v>0.919642857142857</v>
+        <v>0.875739644970414</v>
       </c>
     </row>
     <row r="3">
@@ -567,14 +549,14 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0833309668639855</v>
+        <v>0.0501171383738601</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="n">
-        <v>0.282384282384282</v>
+        <v>0.490842490842491</v>
       </c>
       <c r="G3" t="n">
-        <v>0.84894053315106</v>
+        <v>0.8998778998779</v>
       </c>
     </row>
     <row r="4">
@@ -588,14 +570,14 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0268819224796873</v>
+        <v>-0.00679557008092932</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.851814851814852</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.969306555513452</v>
       </c>
     </row>
     <row r="5">
@@ -609,14 +591,14 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0499440739438321</v>
+        <v>0.0925787219649945</v>
       </c>
       <c r="E5"/>
       <c r="F5" t="n">
-        <v>0.490842490842491</v>
+        <v>0.344988344988345</v>
       </c>
       <c r="G5" t="n">
-        <v>0.87012987012987</v>
+        <v>0.875739644970414</v>
       </c>
     </row>
     <row r="6">
@@ -630,14 +612,14 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.218463075216328</v>
+        <v>-0.228924866458844</v>
       </c>
       <c r="E6"/>
       <c r="F6" t="n">
         <v>0.282384282384282</v>
       </c>
       <c r="G6" t="n">
-        <v>0.84894053315106</v>
+        <v>0.875739644970414</v>
       </c>
     </row>
     <row r="7">
@@ -651,14 +633,14 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.141996769721301</v>
+        <v>-0.108720518773039</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="n">
-        <v>0.490842490842491</v>
+        <v>0.754578754578755</v>
       </c>
       <c r="G7" t="n">
-        <v>0.87012987012987</v>
+        <v>0.957734573119188</v>
       </c>
     </row>
     <row r="8">
@@ -672,14 +654,14 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.12350239077581</v>
+        <v>-0.0229149613392472</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="n">
-        <v>0.572760572760573</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.919642857142857</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -693,14 +675,14 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0589187022083458</v>
+        <v>-0.111793219561234</v>
       </c>
       <c r="E9"/>
       <c r="F9" t="n">
         <v>0.754578754578755</v>
       </c>
       <c r="G9" t="n">
-        <v>0.919642857142857</v>
+        <v>0.957734573119188</v>
       </c>
     </row>
     <row r="10">
@@ -714,14 +696,14 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0990551186554174</v>
+        <v>0.00530669016046955</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="n">
-        <v>0.413586413586414</v>
+        <v>0.94971694971695</v>
       </c>
       <c r="G10" t="n">
-        <v>0.84894053315106</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -735,14 +717,14 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0226234394869827</v>
+        <v>-0.0136095163704868</v>
       </c>
       <c r="E11"/>
       <c r="F11" t="n">
         <v>0.413586413586414</v>
       </c>
       <c r="G11" t="n">
-        <v>0.84894053315106</v>
+        <v>0.8998778998779</v>
       </c>
     </row>
     <row r="12">
@@ -756,14 +738,14 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0694192951965846</v>
+        <v>-0.0134119688794098</v>
       </c>
       <c r="E12"/>
       <c r="F12" t="n">
-        <v>0.490842490842491</v>
+        <v>0.851814851814852</v>
       </c>
       <c r="G12" t="n">
-        <v>0.87012987012987</v>
+        <v>0.969306555513452</v>
       </c>
     </row>
     <row r="13">
@@ -777,14 +759,14 @@
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0207123068790615</v>
+        <v>-0.0375794882770218</v>
       </c>
       <c r="E13"/>
       <c r="F13" t="n">
-        <v>0.413586413586414</v>
+        <v>0.662004662004662</v>
       </c>
       <c r="G13" t="n">
-        <v>0.84894053315106</v>
+        <v>0.957734573119188</v>
       </c>
     </row>
     <row r="14">
@@ -798,14 +780,14 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.00704518930347499</v>
+        <v>0.052111134230586</v>
       </c>
       <c r="E14"/>
       <c r="F14" t="n">
-        <v>0.851814851814852</v>
+        <v>0.181152181152181</v>
       </c>
       <c r="G14" t="n">
-        <v>0.949165120593692</v>
+        <v>0.875739644970414</v>
       </c>
     </row>
     <row r="15">
@@ -819,14 +801,14 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.00000830416504589426</v>
+        <v>0.0325882951203786</v>
       </c>
       <c r="E15"/>
       <c r="F15" t="n">
-        <v>0.94971694971695</v>
+        <v>0.344988344988345</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0.875739644970414</v>
       </c>
     </row>
     <row r="16">
@@ -840,14 +822,14 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0306757238392041</v>
+        <v>-0.0448926621715157</v>
       </c>
       <c r="E16"/>
       <c r="F16" t="n">
-        <v>0.851814851814852</v>
+        <v>0.754578754578755</v>
       </c>
       <c r="G16" t="n">
-        <v>0.949165120593692</v>
+        <v>0.957734573119188</v>
       </c>
     </row>
     <row r="17">
@@ -861,14 +843,14 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.040671375353443</v>
+        <v>-0.0746461918460294</v>
       </c>
       <c r="E17"/>
       <c r="F17" t="n">
-        <v>0.413586413586414</v>
+        <v>0.490842490842491</v>
       </c>
       <c r="G17" t="n">
-        <v>0.84894053315106</v>
+        <v>0.8998778998779</v>
       </c>
     </row>
     <row r="18">
@@ -882,14 +864,14 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0538830114966798</v>
+        <v>-0.00497165768536351</v>
       </c>
       <c r="E18"/>
       <c r="F18" t="n">
-        <v>0.141858141858142</v>
+        <v>0.851814851814852</v>
       </c>
       <c r="G18" t="n">
-        <v>0.84894053315106</v>
+        <v>0.969306555513452</v>
       </c>
     </row>
     <row r="19">
@@ -903,14 +885,14 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0715045914775716</v>
+        <v>0.000410762953521951</v>
       </c>
       <c r="E19"/>
       <c r="F19" t="n">
-        <v>0.413586413586414</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0.84894053315106</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -924,14 +906,14 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>0.189380510961924</v>
+        <v>0.0286368118276565</v>
       </c>
       <c r="E20"/>
       <c r="F20" t="n">
-        <v>0.344988344988345</v>
+        <v>0.490842490842491</v>
       </c>
       <c r="G20" t="n">
-        <v>0.84894053315106</v>
+        <v>0.8998778998779</v>
       </c>
     </row>
     <row r="21">
@@ -945,14 +927,14 @@
         <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0217396628086925</v>
+        <v>0.0489401880745798</v>
       </c>
       <c r="E21"/>
       <c r="F21" t="n">
-        <v>0.754578754578755</v>
+        <v>0.344988344988345</v>
       </c>
       <c r="G21" t="n">
-        <v>0.919642857142857</v>
+        <v>0.875739644970414</v>
       </c>
     </row>
     <row r="22">
@@ -966,14 +948,14 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0800557353378489</v>
+        <v>-0.160442024804595</v>
       </c>
       <c r="E22"/>
       <c r="F22" t="n">
         <v>0.754578754578755</v>
       </c>
       <c r="G22" t="n">
-        <v>0.919642857142857</v>
+        <v>0.957734573119188</v>
       </c>
     </row>
     <row r="23">
@@ -987,14 +969,14 @@
         <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0633615550466427</v>
+        <v>-0.0733787177187182</v>
       </c>
       <c r="E23"/>
       <c r="F23" t="n">
-        <v>0.572760572760573</v>
+        <v>0.344988344988345</v>
       </c>
       <c r="G23" t="n">
-        <v>0.919642857142857</v>
+        <v>0.875739644970414</v>
       </c>
     </row>
     <row r="24">
@@ -1008,14 +990,14 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>0.052422536993431</v>
+        <v>-0.104443599483971</v>
       </c>
       <c r="E24"/>
       <c r="F24" t="n">
-        <v>0.413586413586414</v>
+        <v>0.228438228438228</v>
       </c>
       <c r="G24" t="n">
-        <v>0.84894053315106</v>
+        <v>0.875739644970414</v>
       </c>
     </row>
     <row r="25">
@@ -1029,14 +1011,14 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0286005822554556</v>
+        <v>0.116379868424056</v>
       </c>
       <c r="E25"/>
       <c r="F25" t="n">
-        <v>0.754578754578755</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.919642857142857</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1050,14 +1032,14 @@
         <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.16873198622823</v>
+        <v>-0.122269618514102</v>
       </c>
       <c r="E26"/>
       <c r="F26" t="n">
-        <v>0.754578754578755</v>
+        <v>0.228438228438228</v>
       </c>
       <c r="G26" t="n">
-        <v>0.919642857142857</v>
+        <v>0.875739644970414</v>
       </c>
     </row>
     <row r="27">
@@ -1071,14 +1053,14 @@
         <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>0.070348910894611</v>
+        <v>0.103657042181567</v>
       </c>
       <c r="E27"/>
       <c r="F27" t="n">
-        <v>0.344988344988345</v>
+        <v>0.0812520812520813</v>
       </c>
       <c r="G27" t="n">
-        <v>0.84894053315106</v>
+        <v>0.875739644970414</v>
       </c>
     </row>
     <row r="28">
@@ -1092,14 +1074,14 @@
         <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.00766628887280649</v>
+        <v>-0.0972675702556216</v>
       </c>
       <c r="E28"/>
       <c r="F28" t="n">
-        <v>0.662004662004662</v>
+        <v>0.344988344988345</v>
       </c>
       <c r="G28" t="n">
-        <v>0.919642857142857</v>
+        <v>0.875739644970414</v>
       </c>
     </row>
     <row r="29">
@@ -1113,14 +1095,14 @@
         <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.130515381299885</v>
+        <v>-0.00890608411550463</v>
       </c>
       <c r="E29"/>
       <c r="F29" t="n">
-        <v>0.0592740592740593</v>
+        <v>0.572760572760573</v>
       </c>
       <c r="G29" t="n">
-        <v>0.633766233766234</v>
+        <v>0.957734573119188</v>
       </c>
     </row>
     <row r="30">
@@ -1134,14 +1116,14 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.149335991372548</v>
+        <v>0.189126756038461</v>
       </c>
       <c r="E30"/>
       <c r="F30" t="n">
         <v>0.0592740592740593</v>
       </c>
       <c r="G30" t="n">
-        <v>0.633766233766234</v>
+        <v>0.875739644970414</v>
       </c>
     </row>
     <row r="31">
@@ -1155,14 +1137,14 @@
         <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0817212832296338</v>
+        <v>0.0238922879985101</v>
       </c>
       <c r="E31"/>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0.662004662004662</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0.957734573119188</v>
       </c>
     </row>
     <row r="32">
@@ -1176,14 +1158,14 @@
         <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0831847021760565</v>
+        <v>0.0014771448509598</v>
       </c>
       <c r="E32"/>
       <c r="F32" t="n">
-        <v>0.344988344988345</v>
+        <v>0.662004662004662</v>
       </c>
       <c r="G32" t="n">
-        <v>0.84894053315106</v>
+        <v>0.957734573119188</v>
       </c>
     </row>
     <row r="33">
@@ -1197,14 +1179,14 @@
         <v>39</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00696213581180758</v>
+        <v>-0.0120953512099346</v>
       </c>
       <c r="E33"/>
       <c r="F33" t="n">
-        <v>0.754578754578755</v>
+        <v>0.413586413586414</v>
       </c>
       <c r="G33" t="n">
-        <v>0.919642857142857</v>
+        <v>0.8998778998779</v>
       </c>
     </row>
     <row r="34">
@@ -1218,140 +1200,14 @@
         <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0488793001753013</v>
+        <v>-0.159258844664045</v>
       </c>
       <c r="E34"/>
       <c r="F34" t="n">
-        <v>0.228438228438228</v>
+        <v>0.0426240426240426</v>
       </c>
       <c r="G34" t="n">
-        <v>0.84894053315106</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>7</v>
-      </c>
-      <c r="B35" t="n">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.145981007087185</v>
-      </c>
-      <c r="E35"/>
-      <c r="F35" t="n">
-        <v>0.0812520812520813</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.633766233766234</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" t="n">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.108607198889488</v>
-      </c>
-      <c r="E36"/>
-      <c r="F36" t="n">
-        <v>0.0812520812520813</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.633766233766234</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" t="n">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" t="n">
-        <v>-0.00671763605551619</v>
-      </c>
-      <c r="E37"/>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" t="n">
-        <v>14</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.181998328160775</v>
-      </c>
-      <c r="E38"/>
-      <c r="F38" t="n">
-        <v>0.0812520812520813</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.633766233766234</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" t="n">
-        <v>14</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-0.0154520495888356</v>
-      </c>
-      <c r="E39"/>
-      <c r="F39" t="n">
-        <v>0.413586413586414</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.84894053315106</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" t="n">
-        <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.00150519659723146</v>
-      </c>
-      <c r="E40"/>
-      <c r="F40" t="n">
-        <v>0.851814851814852</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.949165120593692</v>
+        <v>0.875739644970414</v>
       </c>
     </row>
   </sheetData>
@@ -1367,54 +1223,54 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0633615550466427</v>
+        <v>0.0501171383738601</v>
       </c>
     </row>
   </sheetData>
